--- a/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/region-de-coquimbo.xlsx
+++ b/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/region-de-coquimbo.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>3754-179-CM26</t>
+          <t>5416-100-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,27 +524,27 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2025-01-29</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>69.041.300-0</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CANELA</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>ANALYZE CONSULTORIA Y DESARROLLO SPA</t>
+          <t>SONDA S A</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>77.592.300-8</t>
+          <t>83.628.100-4</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>14674.4</v>
+        <v>12419.93</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1305532-67-CM26</t>
+          <t>2147-43-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,27 +585,27 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2025-02-07</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>61.981.040-6</t>
+          <t>61.606.406-1</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DEL ELQUI</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL COMB</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>NAPSIS SPA.</t>
+          <t>Georg</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>76.093.358-9</t>
+          <t>76.624.276-6</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,6 +630,311 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
+        <v>26993.62</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2450-241-CM25</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>abr-2025</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2025-04-24</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>69.040.100-2</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>ILUSTRE MUNICIPALIDAD DE LA SERENA</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Coquimbo </t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>IMPACTE SPA</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>76.572.009-5</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="n">
+        <v>11804.32</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>1588-128-CM25</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>jun-2025</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>72.443.600-5</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>SERVICIO DE EVALUACION AMBIENTAL</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Coquimbo </t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>EVOLUCION, TRANSFORMACION Y CAMBIO CONSULTORES SPA</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>76.444.489-2</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="n">
+        <v>32097.8</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>624-316-CM25</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>72.225.700-6</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>GOBIERNO REGIONAL IV REGION COQUIMBO</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Coquimbo </t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Zecovery Ltda   -    EXEC</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>76.260.080-3</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="n">
+        <v>57729.28</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>3754-179-CM26</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>69.041.300-0</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CANELA</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Coquimbo </t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>ANALYZE CONSULTORIA Y DESARROLLO SPA</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>77.592.300-8</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="n">
+        <v>14674.4</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>1305532-67-CM26</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>61.981.040-6</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DEL ELQUI</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Coquimbo </t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>NAPSIS SPA.</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>76.093.358-9</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="n">
         <v>55513.17</v>
       </c>
     </row>
